--- a/SC Fibb/Book1.xlsx
+++ b/SC Fibb/Book1.xlsx
@@ -1,20 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\AURA\SC Fibb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{649E8A01-FF0F-42D8-9B2E-8A71300AA538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D60F36-2247-4051-B932-BECA6498D91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{F376AF4D-34B0-4633-9DED-70F80F4BDBF8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" firstSheet="1" activeTab="5" xr2:uid="{F376AF4D-34B0-4633-9DED-70F80F4BDBF8}"/>
   </bookViews>
   <sheets>
     <sheet name="About 10 Input" sheetId="1" r:id="rId1"/>
     <sheet name="About 13.5V Input" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId5"/>
+    <sheet name="Sheet4" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="32">
   <si>
     <t xml:space="preserve">Input </t>
   </si>
@@ -62,9 +66,6 @@
   </si>
   <si>
     <t>4 ohms output</t>
-  </si>
-  <si>
-    <t>2 ohms output</t>
   </si>
   <si>
     <t>3 ohms output</t>
@@ -104,6 +105,36 @@
   </si>
   <si>
     <t>4V output after cap added</t>
+  </si>
+  <si>
+    <t>pic 8</t>
+  </si>
+  <si>
+    <t>pic 9</t>
+  </si>
+  <si>
+    <t>pic 10</t>
+  </si>
+  <si>
+    <t>pic 12</t>
+  </si>
+  <si>
+    <t>pic 13</t>
+  </si>
+  <si>
+    <t>pic 14</t>
+  </si>
+  <si>
+    <t>s/p</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>p/s</t>
+  </si>
+  <si>
+    <t>Power Loss (W)</t>
   </si>
 </sst>
 </file>
@@ -145,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -155,6 +186,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -286,28 +335,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>3.2040131999999995</c:v>
+                  <c:v>2.6631</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.100651</c:v>
+                  <c:v>4.4796000000000005</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.3865459999999992</c:v>
+                  <c:v>5.4265740000000005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.3816519999999999</c:v>
+                  <c:v>6.511298</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.8456650000000003</c:v>
+                  <c:v>7.6229870000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>10.107414</c:v>
+                  <c:v>10.017790000000002</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>14.530808</c:v>
+                  <c:v>13.53125</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>25.422519999999999</c:v>
+                  <c:v>20.930800000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -319,28 +368,28 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>0.81527053435114483</c:v>
+                  <c:v>0.93629363991140169</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.87422739095211699</c:v>
+                  <c:v>0.96705669012564233</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.90392408612821884</c:v>
+                  <c:v>0.97672627918529564</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.91873833158847018</c:v>
+                  <c:v>0.97747423570297309</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.93254098434700072</c:v>
+                  <c:v>0.97713089371930517</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.93830622379659512</c:v>
+                  <c:v>0.96887128674568312</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.95036605044338363</c:v>
+                  <c:v>0.97093840097701956</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.92520054700062393</c:v>
+                  <c:v>0.964405445802762</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1117,6 +1166,510 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Duty</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Cycle</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t> = 0.5</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> / </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>deadtimes = 7.5ns </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$K$3:$K$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2.6631</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.4796000000000005</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.4265740000000005</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.511298</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.6229870000000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10.017790000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>13.53125</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20.930800000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>26.331990000000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>32.133200000000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>34.420279999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$M$3:$M$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0.93629363991140169</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96705669012564233</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.97672627918529564</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.97747423570297309</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.97713089371930517</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.96887128674568312</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.97093840097701956</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.964405445802762</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.94600457338705468</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.95251928563128585</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.94592133142428425</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-83E3-47E1-A1AB-96CC3E5A372E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1578310271"/>
+        <c:axId val="1578301119"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1578310271"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Output</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> Power (W)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1578301119"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1578301119"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Efficiency (%)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1578310271"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1197,6 +1750,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -1714,6 +2307,522 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2291,6 +3400,49 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFE4255E-9F6D-4038-898B-048BEC317CF7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{734C18C3-A78B-4389-B77D-E34ABC11D9FA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2629,21 +3781,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
       <c r="J1" t="s">
         <v>1</v>
       </c>
@@ -2654,89 +3806,89 @@
         <v>3</v>
       </c>
       <c r="M1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
       <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
       <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
         <v>12</v>
       </c>
-      <c r="I2" t="s">
-        <v>13</v>
-      </c>
       <c r="J2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" t="s">
         <v>18</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="B3" s="2">
-        <v>0.39300000000000002</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="C3" s="2">
         <f>A3*B3</f>
-        <v>3.93</v>
+        <v>2.8443000000000001</v>
       </c>
       <c r="D3" s="2">
-        <v>4.0119999999999996</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="E3" s="2">
-        <v>0.40089999999999998</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="F3" s="2">
         <f>D3*E3</f>
-        <v>1.6084107999999997</v>
+        <v>1.3065</v>
       </c>
       <c r="G3" s="2">
-        <v>3.9969999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="H3" s="2">
-        <v>0.3992</v>
+        <v>0.32300000000000001</v>
       </c>
       <c r="I3" s="2">
         <f>G3*H3</f>
-        <v>1.5956024</v>
+        <v>1.3566</v>
       </c>
       <c r="J3" s="2">
         <f>C3</f>
-        <v>3.93</v>
+        <v>2.8443000000000001</v>
       </c>
       <c r="K3" s="2">
         <f>F3+I3</f>
-        <v>3.2040131999999995</v>
+        <v>2.6631</v>
       </c>
       <c r="L3" s="4">
         <f>K3/J3</f>
-        <v>0.81527053435114483</v>
+        <v>0.93629363991140169</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>5</v>
@@ -2744,140 +3896,140 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>9.98</v>
+        <v>10.07</v>
       </c>
       <c r="B4" s="2">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="C4" s="2">
         <f t="shared" ref="C4:C10" si="0">A4*B4</f>
-        <v>4.6905999999999999</v>
+        <v>4.6322000000000001</v>
       </c>
       <c r="D4" s="2">
-        <v>4.13</v>
+        <v>4.05</v>
       </c>
       <c r="E4" s="2">
-        <v>0.49840000000000001</v>
+        <v>0.54400000000000004</v>
       </c>
       <c r="F4" s="2">
         <f t="shared" ref="F4:F10" si="1">D4*E4</f>
-        <v>2.058392</v>
+        <v>2.2032000000000003</v>
       </c>
       <c r="G4" s="2">
-        <v>4.1100000000000003</v>
+        <v>4.2</v>
       </c>
       <c r="H4" s="2">
-        <v>0.49690000000000001</v>
+        <v>0.54200000000000004</v>
       </c>
       <c r="I4" s="2">
         <f t="shared" ref="I4:I10" si="2">G4*H4</f>
-        <v>2.042259</v>
+        <v>2.2764000000000002</v>
       </c>
       <c r="J4" s="2">
         <f t="shared" ref="J4:J10" si="3">C4</f>
-        <v>4.6905999999999999</v>
+        <v>4.6322000000000001</v>
       </c>
       <c r="K4" s="2">
         <f t="shared" ref="K4:K10" si="4">F4+I4</f>
-        <v>4.100651</v>
+        <v>4.4796000000000005</v>
       </c>
       <c r="L4" s="4">
         <f t="shared" ref="L4:L10" si="5">K4/J4</f>
-        <v>0.87422739095211699</v>
+        <v>0.96705669012564233</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>9.9700000000000006</v>
+        <v>10.119999999999999</v>
       </c>
       <c r="B5" s="2">
-        <v>0.59770000000000001</v>
+        <v>0.54900000000000004</v>
       </c>
       <c r="C5" s="2">
         <f t="shared" si="0"/>
-        <v>5.9590690000000004</v>
+        <v>5.5558800000000002</v>
       </c>
       <c r="D5" s="2">
-        <v>4.0999999999999996</v>
+        <v>4.07</v>
       </c>
       <c r="E5" s="2">
-        <v>0.6593</v>
+        <v>0.65500000000000003</v>
       </c>
       <c r="F5" s="2">
         <f t="shared" si="1"/>
-        <v>2.7031299999999998</v>
+        <v>2.6658500000000003</v>
       </c>
       <c r="G5" s="2">
-        <v>4.08</v>
+        <v>4.22</v>
       </c>
       <c r="H5" s="2">
-        <v>0.65769999999999995</v>
+        <v>0.6542</v>
       </c>
       <c r="I5" s="2">
         <f t="shared" si="2"/>
-        <v>2.6834159999999998</v>
+        <v>2.7607239999999997</v>
       </c>
       <c r="J5" s="2">
         <f t="shared" si="3"/>
-        <v>5.9590690000000004</v>
+        <v>5.5558800000000002</v>
       </c>
       <c r="K5" s="2">
         <f t="shared" si="4"/>
-        <v>5.3865459999999992</v>
+        <v>5.4265740000000005</v>
       </c>
       <c r="L5" s="4">
         <f t="shared" si="5"/>
-        <v>0.90392408612821884</v>
+        <v>0.97672627918529564</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>9.9600000000000009</v>
+        <v>10.17</v>
       </c>
       <c r="B6" s="2">
-        <v>0.69740000000000002</v>
+        <v>0.65500000000000003</v>
       </c>
       <c r="C6" s="2">
         <f t="shared" si="0"/>
-        <v>6.9461040000000009</v>
+        <v>6.6613500000000005</v>
       </c>
       <c r="D6" s="2">
         <v>4.07</v>
       </c>
       <c r="E6" s="2">
-        <v>0.78580000000000005</v>
+        <v>0.78600000000000003</v>
       </c>
       <c r="F6" s="2">
         <f t="shared" si="1"/>
-        <v>3.1982060000000003</v>
+        <v>3.1990200000000004</v>
       </c>
       <c r="G6" s="2">
-        <v>4.0599999999999996</v>
+        <v>4.22</v>
       </c>
       <c r="H6" s="2">
-        <v>0.78410000000000002</v>
+        <v>0.78490000000000004</v>
       </c>
       <c r="I6" s="2">
         <f t="shared" si="2"/>
-        <v>3.1834459999999996</v>
+        <v>3.3122780000000001</v>
       </c>
       <c r="J6" s="2">
         <f t="shared" si="3"/>
-        <v>6.9461040000000009</v>
+        <v>6.6613500000000005</v>
       </c>
       <c r="K6" s="2">
         <f t="shared" si="4"/>
-        <v>6.3816519999999999</v>
+        <v>6.511298</v>
       </c>
       <c r="L6" s="4">
         <f t="shared" si="5"/>
-        <v>0.91873833158847018</v>
+        <v>0.97747423570297309</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>7</v>
@@ -2885,46 +4037,46 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>9.9600000000000009</v>
+        <v>10.23</v>
       </c>
       <c r="B7" s="2">
-        <v>0.84470000000000001</v>
+        <v>0.76259999999999994</v>
       </c>
       <c r="C7" s="2">
         <f t="shared" si="0"/>
-        <v>8.4132120000000015</v>
+        <v>7.8013979999999998</v>
       </c>
       <c r="D7" s="2">
-        <v>4.04</v>
+        <v>4.07</v>
       </c>
       <c r="E7" s="2">
-        <v>0.97330000000000005</v>
+        <v>0.92010000000000003</v>
       </c>
       <c r="F7" s="2">
         <f t="shared" si="1"/>
-        <v>3.9321320000000002</v>
+        <v>3.7448070000000002</v>
       </c>
       <c r="G7" s="2">
-        <v>4.03</v>
+        <v>4.22</v>
       </c>
       <c r="H7" s="2">
-        <v>0.97109999999999996</v>
+        <v>0.91900000000000004</v>
       </c>
       <c r="I7" s="2">
         <f t="shared" si="2"/>
-        <v>3.9135330000000002</v>
+        <v>3.87818</v>
       </c>
       <c r="J7" s="2">
         <f t="shared" si="3"/>
-        <v>8.4132120000000015</v>
+        <v>7.8013979999999998</v>
       </c>
       <c r="K7" s="2">
         <f t="shared" si="4"/>
-        <v>7.8456650000000003</v>
+        <v>7.6229870000000002</v>
       </c>
       <c r="L7" s="4">
         <f t="shared" si="5"/>
-        <v>0.93254098434700072</v>
+        <v>0.97713089371930517</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>8</v>
@@ -2932,156 +4084,300 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>9.94</v>
+        <v>10.35</v>
       </c>
       <c r="B8" s="2">
-        <v>1.0837000000000001</v>
+        <v>0.999</v>
       </c>
       <c r="C8" s="2">
         <f t="shared" si="0"/>
-        <v>10.771978000000001</v>
+        <v>10.339649999999999</v>
       </c>
       <c r="D8" s="2">
-        <v>3.93</v>
+        <v>4.07</v>
       </c>
       <c r="E8" s="2">
-        <v>1.2777000000000001</v>
+        <v>1.2050000000000001</v>
       </c>
       <c r="F8" s="2">
         <f t="shared" si="1"/>
-        <v>5.0213610000000006</v>
+        <v>4.9043500000000009</v>
       </c>
       <c r="G8" s="2">
-        <v>3.99</v>
+        <v>4.24</v>
       </c>
       <c r="H8" s="2">
-        <v>1.2746999999999999</v>
+        <v>1.206</v>
       </c>
       <c r="I8" s="2">
         <f t="shared" si="2"/>
-        <v>5.0860529999999997</v>
+        <v>5.1134399999999998</v>
       </c>
       <c r="J8" s="2">
         <f t="shared" si="3"/>
-        <v>10.771978000000001</v>
+        <v>10.339649999999999</v>
       </c>
       <c r="K8" s="2">
         <f t="shared" si="4"/>
-        <v>10.107414</v>
+        <v>10.017790000000002</v>
       </c>
       <c r="L8" s="4">
         <f t="shared" si="5"/>
-        <v>0.93830622379659512</v>
+        <v>0.96887128674568312</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>9.92</v>
+        <v>10.51</v>
       </c>
       <c r="B9" s="2">
-        <v>1.5412999999999999</v>
+        <v>1.3260000000000001</v>
       </c>
       <c r="C9" s="2">
         <f t="shared" si="0"/>
-        <v>15.289695999999999</v>
+        <v>13.936260000000001</v>
       </c>
       <c r="D9" s="2">
-        <v>3.86</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="E9" s="2">
-        <v>1.8704000000000001</v>
+        <v>1.62</v>
       </c>
       <c r="F9" s="2">
         <f t="shared" si="1"/>
-        <v>7.2197440000000004</v>
+        <v>6.6419999999999995</v>
       </c>
       <c r="G9" s="2">
-        <v>3.94</v>
+        <v>4.25</v>
       </c>
       <c r="H9" s="2">
-        <v>1.8555999999999999</v>
+        <v>1.621</v>
       </c>
       <c r="I9" s="2">
         <f t="shared" si="2"/>
-        <v>7.311064</v>
+        <v>6.8892499999999997</v>
       </c>
       <c r="J9" s="2">
         <f t="shared" si="3"/>
-        <v>15.289695999999999</v>
+        <v>13.936260000000001</v>
       </c>
       <c r="K9" s="2">
         <f t="shared" si="4"/>
-        <v>14.530808</v>
+        <v>13.53125</v>
       </c>
       <c r="L9" s="4">
         <f t="shared" si="5"/>
-        <v>0.95036605044338363</v>
+        <v>0.97093840097701956</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>9.86</v>
+        <v>10.83</v>
       </c>
       <c r="B10" s="2">
-        <v>2.7867999999999999</v>
+        <v>2.004</v>
       </c>
       <c r="C10" s="2">
         <f t="shared" si="0"/>
-        <v>27.477847999999998</v>
+        <v>21.703320000000001</v>
       </c>
       <c r="D10" s="2">
-        <v>3.65</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="E10" s="2">
-        <v>3.4373</v>
+        <v>2.476</v>
       </c>
       <c r="F10" s="2">
         <f t="shared" si="1"/>
-        <v>12.546144999999999</v>
+        <v>10.275400000000001</v>
       </c>
       <c r="G10" s="2">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="H10" s="2">
-        <v>3.4337</v>
+        <v>2.4780000000000002</v>
       </c>
       <c r="I10" s="2">
         <f t="shared" si="2"/>
-        <v>12.876374999999999</v>
+        <v>10.6554</v>
       </c>
       <c r="J10" s="2">
         <f t="shared" si="3"/>
-        <v>27.477847999999998</v>
+        <v>21.703320000000001</v>
       </c>
       <c r="K10" s="2">
         <f t="shared" si="4"/>
-        <v>25.422519999999999</v>
+        <v>20.930800000000001</v>
       </c>
       <c r="L10" s="4">
         <f t="shared" si="5"/>
-        <v>0.92520054700062393</v>
+        <v>0.964405445802762</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L11" s="1"/>
+      <c r="A11" s="5">
+        <v>11.05</v>
+      </c>
+      <c r="B11" s="5">
+        <v>2.5190000000000001</v>
+      </c>
+      <c r="C11" s="5">
+        <f t="shared" ref="C11:C12" si="6">A11*B11</f>
+        <v>27.834950000000003</v>
+      </c>
+      <c r="D11" s="5">
+        <v>4.16</v>
+      </c>
+      <c r="E11" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="F11" s="5">
+        <f t="shared" ref="F11:F12" si="7">D11*E11</f>
+        <v>12.896000000000001</v>
+      </c>
+      <c r="G11" s="5">
+        <v>4.33</v>
+      </c>
+      <c r="H11" s="5">
+        <v>3.1030000000000002</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" ref="I11:I12" si="8">G11*H11</f>
+        <v>13.43599</v>
+      </c>
+      <c r="J11" s="5">
+        <f t="shared" ref="J11:J12" si="9">C11</f>
+        <v>27.834950000000003</v>
+      </c>
+      <c r="K11" s="5">
+        <f t="shared" ref="K11:K12" si="10">F11+I11</f>
+        <v>26.331990000000001</v>
+      </c>
+      <c r="L11" s="4">
+        <f t="shared" ref="L11:L12" si="11">K11/J11</f>
+        <v>0.94600457338705468</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L12" s="1"/>
+      <c r="A12" s="5">
+        <v>11.26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>2.996</v>
+      </c>
+      <c r="C12" s="5">
+        <f t="shared" si="6"/>
+        <v>33.734960000000001</v>
+      </c>
+      <c r="D12" s="5">
+        <v>4.24</v>
+      </c>
+      <c r="E12" s="5">
+        <v>3.7090000000000001</v>
+      </c>
+      <c r="F12" s="5">
+        <f t="shared" si="7"/>
+        <v>15.726160000000002</v>
+      </c>
+      <c r="G12" s="5">
+        <v>4.42</v>
+      </c>
+      <c r="H12" s="5">
+        <v>3.7120000000000002</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="8"/>
+        <v>16.407040000000002</v>
+      </c>
+      <c r="J12" s="5">
+        <f t="shared" si="9"/>
+        <v>33.734960000000001</v>
+      </c>
+      <c r="K12" s="5">
+        <f t="shared" si="10"/>
+        <v>32.133200000000002</v>
+      </c>
+      <c r="L12" s="4">
+        <f t="shared" si="11"/>
+        <v>0.95251928563128585</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L13" s="1"/>
+      <c r="A13" s="5">
+        <v>11.35</v>
+      </c>
+      <c r="B13" s="5">
+        <v>3.206</v>
+      </c>
+      <c r="C13" s="5">
+        <f t="shared" ref="C13" si="12">A13*B13</f>
+        <v>36.388100000000001</v>
+      </c>
+      <c r="D13" s="5">
+        <v>4.24</v>
+      </c>
+      <c r="E13" s="5">
+        <v>3.968</v>
+      </c>
+      <c r="F13" s="5">
+        <f t="shared" ref="F13" si="13">D13*E13</f>
+        <v>16.82432</v>
+      </c>
+      <c r="G13" s="5">
+        <v>4.43</v>
+      </c>
+      <c r="H13" s="5">
+        <v>3.972</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" ref="I13" si="14">G13*H13</f>
+        <v>17.595959999999998</v>
+      </c>
+      <c r="J13" s="5">
+        <f t="shared" ref="J13" si="15">C13</f>
+        <v>36.388100000000001</v>
+      </c>
+      <c r="K13" s="5">
+        <f t="shared" ref="K13" si="16">F13+I13</f>
+        <v>34.420279999999998</v>
+      </c>
+      <c r="L13" s="4">
+        <f t="shared" ref="L13" si="17">K13/J13</f>
+        <v>0.94592133142428425</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="L14" s="1"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="5"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="L15" s="1"/>
@@ -3113,6 +4409,7 @@
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="G1:I1"/>
   </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -3139,21 +4436,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
       <c r="J1" t="s">
         <v>1</v>
       </c>
@@ -3164,45 +4461,45 @@
         <v>3</v>
       </c>
       <c r="M1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
       <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
       <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
         <v>12</v>
       </c>
-      <c r="I2" t="s">
-        <v>13</v>
-      </c>
       <c r="J2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" t="s">
         <v>18</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -3484,7 +4781,7 @@
         <v>0.83655866639238852</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -3531,7 +4828,7 @@
         <v>0.84991248672073316</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -3578,7 +4875,7 @@
         <v>0.83741618494428838</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -3603,21 +4900,21 @@
       <c r="L17" s="1"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5" t="s">
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
       <c r="J18" t="s">
         <v>1</v>
       </c>
@@ -3628,45 +4925,45 @@
         <v>3</v>
       </c>
       <c r="M18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" t="s">
         <v>12</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>13</v>
       </c>
-      <c r="D19" t="s">
-        <v>14</v>
-      </c>
       <c r="E19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" t="s">
         <v>12</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>13</v>
       </c>
-      <c r="G19" t="s">
-        <v>14</v>
-      </c>
       <c r="H19" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" t="s">
         <v>12</v>
       </c>
-      <c r="I19" t="s">
-        <v>13</v>
-      </c>
       <c r="J19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K19" t="s">
+        <v>17</v>
+      </c>
+      <c r="L19" t="s">
         <v>18</v>
-      </c>
-      <c r="L19" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -3713,7 +5010,7 @@
         <v>0.92520054700062393</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -3760,7 +5057,7 @@
         <v>0.95069539566733374</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -3779,4 +5076,2755 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AD99EF4-7713-43E8-A6D6-ED33F794BDED}">
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="24.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>9.98</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="C3" s="5">
+        <f>A3*B3</f>
+        <v>2.8443000000000001</v>
+      </c>
+      <c r="D3" s="5">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="F3" s="5">
+        <f>D3*E3</f>
+        <v>1.3065</v>
+      </c>
+      <c r="G3" s="5">
+        <v>4.2</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0.32300000000000001</v>
+      </c>
+      <c r="I3" s="5">
+        <f>G3*H3</f>
+        <v>1.3566</v>
+      </c>
+      <c r="J3" s="5">
+        <f>C3</f>
+        <v>2.8443000000000001</v>
+      </c>
+      <c r="K3" s="5">
+        <f>F3+I3</f>
+        <v>2.6631</v>
+      </c>
+      <c r="L3" s="7">
+        <f>J3-K3</f>
+        <v>0.18120000000000003</v>
+      </c>
+      <c r="M3" s="4">
+        <f>K3/J3</f>
+        <v>0.93629363991140169</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>10.07</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0.46</v>
+      </c>
+      <c r="C4" s="5">
+        <f t="shared" ref="C4:C13" si="0">A4*B4</f>
+        <v>4.6322000000000001</v>
+      </c>
+      <c r="D4" s="5">
+        <v>4.05</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0.54400000000000004</v>
+      </c>
+      <c r="F4" s="5">
+        <f t="shared" ref="F4:F13" si="1">D4*E4</f>
+        <v>2.2032000000000003</v>
+      </c>
+      <c r="G4" s="5">
+        <v>4.2</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="I4" s="5">
+        <f t="shared" ref="I4:I13" si="2">G4*H4</f>
+        <v>2.2764000000000002</v>
+      </c>
+      <c r="J4" s="5">
+        <f t="shared" ref="J4:J13" si="3">C4</f>
+        <v>4.6322000000000001</v>
+      </c>
+      <c r="K4" s="5">
+        <f t="shared" ref="K4:K13" si="4">F4+I4</f>
+        <v>4.4796000000000005</v>
+      </c>
+      <c r="L4" s="7">
+        <f t="shared" ref="L4:L13" si="5">J4-K4</f>
+        <v>0.15259999999999962</v>
+      </c>
+      <c r="M4" s="4">
+        <f t="shared" ref="M4:M13" si="6">K4/J4</f>
+        <v>0.96705669012564233</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>10.119999999999999</v>
+      </c>
+      <c r="B5" s="5">
+        <v>0.54900000000000004</v>
+      </c>
+      <c r="C5" s="5">
+        <f t="shared" si="0"/>
+        <v>5.5558800000000002</v>
+      </c>
+      <c r="D5" s="5">
+        <v>4.07</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0.65500000000000003</v>
+      </c>
+      <c r="F5" s="5">
+        <f t="shared" si="1"/>
+        <v>2.6658500000000003</v>
+      </c>
+      <c r="G5" s="5">
+        <v>4.22</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0.6542</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" si="2"/>
+        <v>2.7607239999999997</v>
+      </c>
+      <c r="J5" s="5">
+        <f t="shared" si="3"/>
+        <v>5.5558800000000002</v>
+      </c>
+      <c r="K5" s="5">
+        <f t="shared" si="4"/>
+        <v>5.4265740000000005</v>
+      </c>
+      <c r="L5" s="7">
+        <f t="shared" si="5"/>
+        <v>0.1293059999999997</v>
+      </c>
+      <c r="M5" s="4">
+        <f t="shared" si="6"/>
+        <v>0.97672627918529564</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>10.17</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0.65500000000000003</v>
+      </c>
+      <c r="C6" s="5">
+        <f t="shared" si="0"/>
+        <v>6.6613500000000005</v>
+      </c>
+      <c r="D6" s="5">
+        <v>4.07</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0.78600000000000003</v>
+      </c>
+      <c r="F6" s="5">
+        <f t="shared" si="1"/>
+        <v>3.1990200000000004</v>
+      </c>
+      <c r="G6" s="5">
+        <v>4.22</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0.78490000000000004</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="2"/>
+        <v>3.3122780000000001</v>
+      </c>
+      <c r="J6" s="5">
+        <f t="shared" si="3"/>
+        <v>6.6613500000000005</v>
+      </c>
+      <c r="K6" s="5">
+        <f t="shared" si="4"/>
+        <v>6.511298</v>
+      </c>
+      <c r="L6" s="7">
+        <f t="shared" si="5"/>
+        <v>0.15005200000000052</v>
+      </c>
+      <c r="M6" s="4">
+        <f t="shared" si="6"/>
+        <v>0.97747423570297309</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>10.23</v>
+      </c>
+      <c r="B7" s="5">
+        <v>0.76259999999999994</v>
+      </c>
+      <c r="C7" s="5">
+        <f t="shared" si="0"/>
+        <v>7.8013979999999998</v>
+      </c>
+      <c r="D7" s="5">
+        <v>4.07</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0.92010000000000003</v>
+      </c>
+      <c r="F7" s="5">
+        <f t="shared" si="1"/>
+        <v>3.7448070000000002</v>
+      </c>
+      <c r="G7" s="5">
+        <v>4.22</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0.91900000000000004</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="2"/>
+        <v>3.87818</v>
+      </c>
+      <c r="J7" s="5">
+        <f t="shared" si="3"/>
+        <v>7.8013979999999998</v>
+      </c>
+      <c r="K7" s="5">
+        <f t="shared" si="4"/>
+        <v>7.6229870000000002</v>
+      </c>
+      <c r="L7" s="7">
+        <f t="shared" si="5"/>
+        <v>0.17841099999999965</v>
+      </c>
+      <c r="M7" s="4">
+        <f t="shared" si="6"/>
+        <v>0.97713089371930517</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>10.35</v>
+      </c>
+      <c r="B8" s="5">
+        <v>0.999</v>
+      </c>
+      <c r="C8" s="5">
+        <f t="shared" si="0"/>
+        <v>10.339649999999999</v>
+      </c>
+      <c r="D8" s="5">
+        <v>4.07</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1.2050000000000001</v>
+      </c>
+      <c r="F8" s="5">
+        <f t="shared" si="1"/>
+        <v>4.9043500000000009</v>
+      </c>
+      <c r="G8" s="5">
+        <v>4.24</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1.206</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="2"/>
+        <v>5.1134399999999998</v>
+      </c>
+      <c r="J8" s="5">
+        <f t="shared" si="3"/>
+        <v>10.339649999999999</v>
+      </c>
+      <c r="K8" s="5">
+        <f t="shared" si="4"/>
+        <v>10.017790000000002</v>
+      </c>
+      <c r="L8" s="7">
+        <f t="shared" si="5"/>
+        <v>0.32185999999999737</v>
+      </c>
+      <c r="M8" s="4">
+        <f t="shared" si="6"/>
+        <v>0.96887128674568312</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>10.51</v>
+      </c>
+      <c r="B9" s="5">
+        <v>1.3260000000000001</v>
+      </c>
+      <c r="C9" s="5">
+        <f t="shared" si="0"/>
+        <v>13.936260000000001</v>
+      </c>
+      <c r="D9" s="5">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1.62</v>
+      </c>
+      <c r="F9" s="5">
+        <f t="shared" si="1"/>
+        <v>6.6419999999999995</v>
+      </c>
+      <c r="G9" s="5">
+        <v>4.25</v>
+      </c>
+      <c r="H9" s="5">
+        <v>1.621</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="2"/>
+        <v>6.8892499999999997</v>
+      </c>
+      <c r="J9" s="5">
+        <f t="shared" si="3"/>
+        <v>13.936260000000001</v>
+      </c>
+      <c r="K9" s="5">
+        <f t="shared" si="4"/>
+        <v>13.53125</v>
+      </c>
+      <c r="L9" s="7">
+        <f t="shared" si="5"/>
+        <v>0.40501000000000076</v>
+      </c>
+      <c r="M9" s="4">
+        <f t="shared" si="6"/>
+        <v>0.97093840097701956</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>10.83</v>
+      </c>
+      <c r="B10" s="5">
+        <v>2.004</v>
+      </c>
+      <c r="C10" s="5">
+        <f t="shared" si="0"/>
+        <v>21.703320000000001</v>
+      </c>
+      <c r="D10" s="5">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="E10" s="5">
+        <v>2.476</v>
+      </c>
+      <c r="F10" s="5">
+        <f t="shared" si="1"/>
+        <v>10.275400000000001</v>
+      </c>
+      <c r="G10" s="5">
+        <v>4.3</v>
+      </c>
+      <c r="H10" s="5">
+        <v>2.4780000000000002</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="2"/>
+        <v>10.6554</v>
+      </c>
+      <c r="J10" s="5">
+        <f t="shared" si="3"/>
+        <v>21.703320000000001</v>
+      </c>
+      <c r="K10" s="5">
+        <f t="shared" si="4"/>
+        <v>20.930800000000001</v>
+      </c>
+      <c r="L10" s="7">
+        <f t="shared" si="5"/>
+        <v>0.7725200000000001</v>
+      </c>
+      <c r="M10" s="4">
+        <f t="shared" si="6"/>
+        <v>0.964405445802762</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>11.05</v>
+      </c>
+      <c r="B11" s="5">
+        <v>2.5190000000000001</v>
+      </c>
+      <c r="C11" s="5">
+        <f t="shared" si="0"/>
+        <v>27.834950000000003</v>
+      </c>
+      <c r="D11" s="5">
+        <v>4.16</v>
+      </c>
+      <c r="E11" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="F11" s="5">
+        <f t="shared" si="1"/>
+        <v>12.896000000000001</v>
+      </c>
+      <c r="G11" s="5">
+        <v>4.33</v>
+      </c>
+      <c r="H11" s="5">
+        <v>3.1030000000000002</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="2"/>
+        <v>13.43599</v>
+      </c>
+      <c r="J11" s="5">
+        <f t="shared" si="3"/>
+        <v>27.834950000000003</v>
+      </c>
+      <c r="K11" s="5">
+        <f t="shared" si="4"/>
+        <v>26.331990000000001</v>
+      </c>
+      <c r="L11" s="7">
+        <f t="shared" si="5"/>
+        <v>1.5029600000000016</v>
+      </c>
+      <c r="M11" s="4">
+        <f t="shared" si="6"/>
+        <v>0.94600457338705468</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>11.26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>2.996</v>
+      </c>
+      <c r="C12" s="5">
+        <f t="shared" si="0"/>
+        <v>33.734960000000001</v>
+      </c>
+      <c r="D12" s="5">
+        <v>4.24</v>
+      </c>
+      <c r="E12" s="5">
+        <v>3.7090000000000001</v>
+      </c>
+      <c r="F12" s="5">
+        <f t="shared" si="1"/>
+        <v>15.726160000000002</v>
+      </c>
+      <c r="G12" s="5">
+        <v>4.42</v>
+      </c>
+      <c r="H12" s="5">
+        <v>3.7120000000000002</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="2"/>
+        <v>16.407040000000002</v>
+      </c>
+      <c r="J12" s="5">
+        <f t="shared" si="3"/>
+        <v>33.734960000000001</v>
+      </c>
+      <c r="K12" s="5">
+        <f t="shared" si="4"/>
+        <v>32.133200000000002</v>
+      </c>
+      <c r="L12" s="7">
+        <f t="shared" si="5"/>
+        <v>1.6017599999999987</v>
+      </c>
+      <c r="M12" s="4">
+        <f t="shared" si="6"/>
+        <v>0.95251928563128585</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>11.35</v>
+      </c>
+      <c r="B13" s="5">
+        <v>3.206</v>
+      </c>
+      <c r="C13" s="5">
+        <f t="shared" si="0"/>
+        <v>36.388100000000001</v>
+      </c>
+      <c r="D13" s="5">
+        <v>4.24</v>
+      </c>
+      <c r="E13" s="5">
+        <v>3.968</v>
+      </c>
+      <c r="F13" s="5">
+        <f t="shared" si="1"/>
+        <v>16.82432</v>
+      </c>
+      <c r="G13" s="5">
+        <v>4.43</v>
+      </c>
+      <c r="H13" s="5">
+        <v>3.972</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="2"/>
+        <v>17.595959999999998</v>
+      </c>
+      <c r="J13" s="5">
+        <f t="shared" si="3"/>
+        <v>36.388100000000001</v>
+      </c>
+      <c r="K13" s="5">
+        <f t="shared" si="4"/>
+        <v>34.420279999999998</v>
+      </c>
+      <c r="L13" s="7">
+        <f t="shared" si="5"/>
+        <v>1.9678200000000032</v>
+      </c>
+      <c r="M13" s="4">
+        <f t="shared" si="6"/>
+        <v>0.94592133142428425</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5329D54-F913-47C2-B69A-515084901F1E}">
+  <dimension ref="A1:M13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>9.98</v>
+      </c>
+      <c r="B3" s="6">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="C3" s="6">
+        <f>A3*B3</f>
+        <v>2.8443000000000001</v>
+      </c>
+      <c r="D3" s="6">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="F3" s="6">
+        <f>D3*E3</f>
+        <v>1.3065</v>
+      </c>
+      <c r="G3" s="6">
+        <v>4.2</v>
+      </c>
+      <c r="H3" s="6">
+        <v>0.32300000000000001</v>
+      </c>
+      <c r="I3" s="6">
+        <f>G3*H3</f>
+        <v>1.3566</v>
+      </c>
+      <c r="J3" s="6">
+        <f>C3</f>
+        <v>2.8443000000000001</v>
+      </c>
+      <c r="K3" s="6">
+        <f>F3+I3</f>
+        <v>2.6631</v>
+      </c>
+      <c r="L3" s="4">
+        <f>K3/J3</f>
+        <v>0.93629363991140169</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>10.07</v>
+      </c>
+      <c r="B4" s="6">
+        <v>0.46</v>
+      </c>
+      <c r="C4" s="6">
+        <f t="shared" ref="C4:C13" si="0">A4*B4</f>
+        <v>4.6322000000000001</v>
+      </c>
+      <c r="D4" s="6">
+        <v>4.05</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0.54400000000000004</v>
+      </c>
+      <c r="F4" s="6">
+        <f t="shared" ref="F4:F13" si="1">D4*E4</f>
+        <v>2.2032000000000003</v>
+      </c>
+      <c r="G4" s="6">
+        <v>4.2</v>
+      </c>
+      <c r="H4" s="6">
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="I4" s="6">
+        <f t="shared" ref="I4:I13" si="2">G4*H4</f>
+        <v>2.2764000000000002</v>
+      </c>
+      <c r="J4" s="6">
+        <f t="shared" ref="J4:J13" si="3">C4</f>
+        <v>4.6322000000000001</v>
+      </c>
+      <c r="K4" s="6">
+        <f t="shared" ref="K4:K13" si="4">F4+I4</f>
+        <v>4.4796000000000005</v>
+      </c>
+      <c r="L4" s="4">
+        <f t="shared" ref="L4:L13" si="5">K4/J4</f>
+        <v>0.96705669012564233</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>10.119999999999999</v>
+      </c>
+      <c r="B5" s="6">
+        <v>0.54900000000000004</v>
+      </c>
+      <c r="C5" s="6">
+        <f t="shared" si="0"/>
+        <v>5.5558800000000002</v>
+      </c>
+      <c r="D5" s="6">
+        <v>4.07</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0.65500000000000003</v>
+      </c>
+      <c r="F5" s="6">
+        <f t="shared" si="1"/>
+        <v>2.6658500000000003</v>
+      </c>
+      <c r="G5" s="6">
+        <v>4.22</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0.6542</v>
+      </c>
+      <c r="I5" s="6">
+        <f t="shared" si="2"/>
+        <v>2.7607239999999997</v>
+      </c>
+      <c r="J5" s="6">
+        <f t="shared" si="3"/>
+        <v>5.5558800000000002</v>
+      </c>
+      <c r="K5" s="6">
+        <f t="shared" si="4"/>
+        <v>5.4265740000000005</v>
+      </c>
+      <c r="L5" s="4">
+        <f t="shared" si="5"/>
+        <v>0.97672627918529564</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>10.17</v>
+      </c>
+      <c r="B6" s="6">
+        <v>0.65500000000000003</v>
+      </c>
+      <c r="C6" s="6">
+        <f t="shared" si="0"/>
+        <v>6.6613500000000005</v>
+      </c>
+      <c r="D6" s="6">
+        <v>4.07</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0.78600000000000003</v>
+      </c>
+      <c r="F6" s="6">
+        <f t="shared" si="1"/>
+        <v>3.1990200000000004</v>
+      </c>
+      <c r="G6" s="6">
+        <v>4.22</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0.78490000000000004</v>
+      </c>
+      <c r="I6" s="6">
+        <f t="shared" si="2"/>
+        <v>3.3122780000000001</v>
+      </c>
+      <c r="J6" s="6">
+        <f t="shared" si="3"/>
+        <v>6.6613500000000005</v>
+      </c>
+      <c r="K6" s="6">
+        <f t="shared" si="4"/>
+        <v>6.511298</v>
+      </c>
+      <c r="L6" s="4">
+        <f t="shared" si="5"/>
+        <v>0.97747423570297309</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>10.23</v>
+      </c>
+      <c r="B7" s="6">
+        <v>0.76259999999999994</v>
+      </c>
+      <c r="C7" s="6">
+        <f t="shared" si="0"/>
+        <v>7.8013979999999998</v>
+      </c>
+      <c r="D7" s="6">
+        <v>4.07</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.92010000000000003</v>
+      </c>
+      <c r="F7" s="6">
+        <f t="shared" si="1"/>
+        <v>3.7448070000000002</v>
+      </c>
+      <c r="G7" s="6">
+        <v>4.22</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0.91900000000000004</v>
+      </c>
+      <c r="I7" s="6">
+        <f t="shared" si="2"/>
+        <v>3.87818</v>
+      </c>
+      <c r="J7" s="6">
+        <f t="shared" si="3"/>
+        <v>7.8013979999999998</v>
+      </c>
+      <c r="K7" s="6">
+        <f t="shared" si="4"/>
+        <v>7.6229870000000002</v>
+      </c>
+      <c r="L7" s="4">
+        <f t="shared" si="5"/>
+        <v>0.97713089371930517</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>10.35</v>
+      </c>
+      <c r="B8" s="6">
+        <v>0.999</v>
+      </c>
+      <c r="C8" s="6">
+        <f t="shared" si="0"/>
+        <v>10.339649999999999</v>
+      </c>
+      <c r="D8" s="6">
+        <v>4.07</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1.2050000000000001</v>
+      </c>
+      <c r="F8" s="6">
+        <f t="shared" si="1"/>
+        <v>4.9043500000000009</v>
+      </c>
+      <c r="G8" s="6">
+        <v>4.24</v>
+      </c>
+      <c r="H8" s="6">
+        <v>1.206</v>
+      </c>
+      <c r="I8" s="6">
+        <f t="shared" si="2"/>
+        <v>5.1134399999999998</v>
+      </c>
+      <c r="J8" s="6">
+        <f t="shared" si="3"/>
+        <v>10.339649999999999</v>
+      </c>
+      <c r="K8" s="6">
+        <f t="shared" si="4"/>
+        <v>10.017790000000002</v>
+      </c>
+      <c r="L8" s="4">
+        <f t="shared" si="5"/>
+        <v>0.96887128674568312</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>10.51</v>
+      </c>
+      <c r="B9" s="6">
+        <v>1.3260000000000001</v>
+      </c>
+      <c r="C9" s="6">
+        <f t="shared" si="0"/>
+        <v>13.936260000000001</v>
+      </c>
+      <c r="D9" s="6">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1.62</v>
+      </c>
+      <c r="F9" s="6">
+        <f t="shared" si="1"/>
+        <v>6.6419999999999995</v>
+      </c>
+      <c r="G9" s="6">
+        <v>4.25</v>
+      </c>
+      <c r="H9" s="6">
+        <v>1.621</v>
+      </c>
+      <c r="I9" s="6">
+        <f t="shared" si="2"/>
+        <v>6.8892499999999997</v>
+      </c>
+      <c r="J9" s="6">
+        <f t="shared" si="3"/>
+        <v>13.936260000000001</v>
+      </c>
+      <c r="K9" s="6">
+        <f t="shared" si="4"/>
+        <v>13.53125</v>
+      </c>
+      <c r="L9" s="4">
+        <f t="shared" si="5"/>
+        <v>0.97093840097701956</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>10.83</v>
+      </c>
+      <c r="B10" s="6">
+        <v>2.004</v>
+      </c>
+      <c r="C10" s="6">
+        <f t="shared" si="0"/>
+        <v>21.703320000000001</v>
+      </c>
+      <c r="D10" s="6">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2.476</v>
+      </c>
+      <c r="F10" s="6">
+        <f t="shared" si="1"/>
+        <v>10.275400000000001</v>
+      </c>
+      <c r="G10" s="6">
+        <v>4.3</v>
+      </c>
+      <c r="H10" s="6">
+        <v>2.4780000000000002</v>
+      </c>
+      <c r="I10" s="6">
+        <f t="shared" si="2"/>
+        <v>10.6554</v>
+      </c>
+      <c r="J10" s="6">
+        <f t="shared" si="3"/>
+        <v>21.703320000000001</v>
+      </c>
+      <c r="K10" s="6">
+        <f t="shared" si="4"/>
+        <v>20.930800000000001</v>
+      </c>
+      <c r="L10" s="4">
+        <f t="shared" si="5"/>
+        <v>0.964405445802762</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>11.05</v>
+      </c>
+      <c r="B11" s="6">
+        <v>2.5190000000000001</v>
+      </c>
+      <c r="C11" s="6">
+        <f t="shared" si="0"/>
+        <v>27.834950000000003</v>
+      </c>
+      <c r="D11" s="6">
+        <v>4.16</v>
+      </c>
+      <c r="E11" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="F11" s="6">
+        <f t="shared" si="1"/>
+        <v>12.896000000000001</v>
+      </c>
+      <c r="G11" s="6">
+        <v>4.33</v>
+      </c>
+      <c r="H11" s="6">
+        <v>3.1030000000000002</v>
+      </c>
+      <c r="I11" s="6">
+        <f t="shared" si="2"/>
+        <v>13.43599</v>
+      </c>
+      <c r="J11" s="6">
+        <f t="shared" si="3"/>
+        <v>27.834950000000003</v>
+      </c>
+      <c r="K11" s="6">
+        <f t="shared" si="4"/>
+        <v>26.331990000000001</v>
+      </c>
+      <c r="L11" s="4">
+        <f t="shared" si="5"/>
+        <v>0.94600457338705468</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>11.26</v>
+      </c>
+      <c r="B12" s="6">
+        <v>2.996</v>
+      </c>
+      <c r="C12" s="6">
+        <f t="shared" si="0"/>
+        <v>33.734960000000001</v>
+      </c>
+      <c r="D12" s="6">
+        <v>4.24</v>
+      </c>
+      <c r="E12" s="6">
+        <v>3.7090000000000001</v>
+      </c>
+      <c r="F12" s="6">
+        <f t="shared" si="1"/>
+        <v>15.726160000000002</v>
+      </c>
+      <c r="G12" s="6">
+        <v>4.42</v>
+      </c>
+      <c r="H12" s="6">
+        <v>3.7120000000000002</v>
+      </c>
+      <c r="I12" s="6">
+        <f t="shared" si="2"/>
+        <v>16.407040000000002</v>
+      </c>
+      <c r="J12" s="6">
+        <f t="shared" si="3"/>
+        <v>33.734960000000001</v>
+      </c>
+      <c r="K12" s="6">
+        <f t="shared" si="4"/>
+        <v>32.133200000000002</v>
+      </c>
+      <c r="L12" s="4">
+        <f t="shared" si="5"/>
+        <v>0.95251928563128585</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>11.35</v>
+      </c>
+      <c r="B13" s="6">
+        <v>3.206</v>
+      </c>
+      <c r="C13" s="6">
+        <f t="shared" si="0"/>
+        <v>36.388100000000001</v>
+      </c>
+      <c r="D13" s="6">
+        <v>4.24</v>
+      </c>
+      <c r="E13" s="6">
+        <v>3.968</v>
+      </c>
+      <c r="F13" s="6">
+        <f t="shared" si="1"/>
+        <v>16.82432</v>
+      </c>
+      <c r="G13" s="6">
+        <v>4.43</v>
+      </c>
+      <c r="H13" s="6">
+        <v>3.972</v>
+      </c>
+      <c r="I13" s="6">
+        <f t="shared" si="2"/>
+        <v>17.595959999999998</v>
+      </c>
+      <c r="J13" s="6">
+        <f t="shared" si="3"/>
+        <v>36.388100000000001</v>
+      </c>
+      <c r="K13" s="6">
+        <f t="shared" si="4"/>
+        <v>34.420279999999998</v>
+      </c>
+      <c r="L13" s="4">
+        <f t="shared" si="5"/>
+        <v>0.94592133142428425</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{925249F9-C649-4C85-84C3-48E2F5D7C119}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C302BADD-3559-4C84-9F4A-75529F60CC45}">
+  <dimension ref="A1:M34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>9.98</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="C3" s="8">
+        <f>A3*B3</f>
+        <v>2.8443000000000001</v>
+      </c>
+      <c r="D3" s="8">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="F3" s="8">
+        <f>D3*E3</f>
+        <v>1.3065</v>
+      </c>
+      <c r="G3" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="H3" s="8">
+        <v>0.32300000000000001</v>
+      </c>
+      <c r="I3" s="8">
+        <f>G3*H3</f>
+        <v>1.3566</v>
+      </c>
+      <c r="J3" s="8">
+        <f>C3</f>
+        <v>2.8443000000000001</v>
+      </c>
+      <c r="K3" s="8">
+        <f>F3+I3</f>
+        <v>2.6631</v>
+      </c>
+      <c r="L3" s="4">
+        <f>K3/J3</f>
+        <v>0.93629363991140169</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <v>10.07</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.46</v>
+      </c>
+      <c r="C4" s="8">
+        <f t="shared" ref="C4:C17" si="0">A4*B4</f>
+        <v>4.6322000000000001</v>
+      </c>
+      <c r="D4" s="8">
+        <v>4.05</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.54400000000000004</v>
+      </c>
+      <c r="F4" s="8">
+        <f t="shared" ref="F4:F17" si="1">D4*E4</f>
+        <v>2.2032000000000003</v>
+      </c>
+      <c r="G4" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="H4" s="8">
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="I4" s="8">
+        <f t="shared" ref="I4:I17" si="2">G4*H4</f>
+        <v>2.2764000000000002</v>
+      </c>
+      <c r="J4" s="8">
+        <f t="shared" ref="J4:J17" si="3">C4</f>
+        <v>4.6322000000000001</v>
+      </c>
+      <c r="K4" s="8">
+        <f t="shared" ref="K4:K17" si="4">F4+I4</f>
+        <v>4.4796000000000005</v>
+      </c>
+      <c r="L4" s="4">
+        <f t="shared" ref="L4:L17" si="5">K4/J4</f>
+        <v>0.96705669012564233</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>10.119999999999999</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.54900000000000004</v>
+      </c>
+      <c r="C5" s="8">
+        <f t="shared" si="0"/>
+        <v>5.5558800000000002</v>
+      </c>
+      <c r="D5" s="8">
+        <v>4.07</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.65500000000000003</v>
+      </c>
+      <c r="F5" s="8">
+        <f t="shared" si="1"/>
+        <v>2.6658500000000003</v>
+      </c>
+      <c r="G5" s="8">
+        <v>4.22</v>
+      </c>
+      <c r="H5" s="8">
+        <v>0.6542</v>
+      </c>
+      <c r="I5" s="8">
+        <f t="shared" si="2"/>
+        <v>2.7607239999999997</v>
+      </c>
+      <c r="J5" s="8">
+        <f t="shared" si="3"/>
+        <v>5.5558800000000002</v>
+      </c>
+      <c r="K5" s="8">
+        <f t="shared" si="4"/>
+        <v>5.4265740000000005</v>
+      </c>
+      <c r="L5" s="4">
+        <f t="shared" si="5"/>
+        <v>0.97672627918529564</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
+        <v>10.17</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.65500000000000003</v>
+      </c>
+      <c r="C6" s="8">
+        <f t="shared" si="0"/>
+        <v>6.6613500000000005</v>
+      </c>
+      <c r="D6" s="8">
+        <v>4.07</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0.78600000000000003</v>
+      </c>
+      <c r="F6" s="8">
+        <f t="shared" si="1"/>
+        <v>3.1990200000000004</v>
+      </c>
+      <c r="G6" s="8">
+        <v>4.22</v>
+      </c>
+      <c r="H6" s="8">
+        <v>0.78490000000000004</v>
+      </c>
+      <c r="I6" s="8">
+        <f t="shared" si="2"/>
+        <v>3.3122780000000001</v>
+      </c>
+      <c r="J6" s="8">
+        <f t="shared" si="3"/>
+        <v>6.6613500000000005</v>
+      </c>
+      <c r="K6" s="8">
+        <f t="shared" si="4"/>
+        <v>6.511298</v>
+      </c>
+      <c r="L6" s="4">
+        <f t="shared" si="5"/>
+        <v>0.97747423570297309</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="8">
+        <v>10.23</v>
+      </c>
+      <c r="B7" s="8">
+        <v>0.76259999999999994</v>
+      </c>
+      <c r="C7" s="8">
+        <f t="shared" si="0"/>
+        <v>7.8013979999999998</v>
+      </c>
+      <c r="D7" s="8">
+        <v>4.07</v>
+      </c>
+      <c r="E7" s="8">
+        <v>0.92010000000000003</v>
+      </c>
+      <c r="F7" s="8">
+        <f t="shared" si="1"/>
+        <v>3.7448070000000002</v>
+      </c>
+      <c r="G7" s="8">
+        <v>4.22</v>
+      </c>
+      <c r="H7" s="8">
+        <v>0.91900000000000004</v>
+      </c>
+      <c r="I7" s="8">
+        <f t="shared" si="2"/>
+        <v>3.87818</v>
+      </c>
+      <c r="J7" s="8">
+        <f t="shared" si="3"/>
+        <v>7.8013979999999998</v>
+      </c>
+      <c r="K7" s="8">
+        <f t="shared" si="4"/>
+        <v>7.6229870000000002</v>
+      </c>
+      <c r="L7" s="4">
+        <f t="shared" si="5"/>
+        <v>0.97713089371930517</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="8">
+        <v>10.35</v>
+      </c>
+      <c r="B8" s="8">
+        <v>0.999</v>
+      </c>
+      <c r="C8" s="8">
+        <f t="shared" si="0"/>
+        <v>10.339649999999999</v>
+      </c>
+      <c r="D8" s="8">
+        <v>4.07</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1.2050000000000001</v>
+      </c>
+      <c r="F8" s="8">
+        <f t="shared" si="1"/>
+        <v>4.9043500000000009</v>
+      </c>
+      <c r="G8" s="8">
+        <v>4.24</v>
+      </c>
+      <c r="H8" s="8">
+        <v>1.206</v>
+      </c>
+      <c r="I8" s="8">
+        <f t="shared" si="2"/>
+        <v>5.1134399999999998</v>
+      </c>
+      <c r="J8" s="8">
+        <f t="shared" si="3"/>
+        <v>10.339649999999999</v>
+      </c>
+      <c r="K8" s="8">
+        <f t="shared" si="4"/>
+        <v>10.017790000000002</v>
+      </c>
+      <c r="L8" s="4">
+        <f t="shared" si="5"/>
+        <v>0.96887128674568312</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="8">
+        <v>10.51</v>
+      </c>
+      <c r="B9" s="8">
+        <v>1.3260000000000001</v>
+      </c>
+      <c r="C9" s="8">
+        <f t="shared" si="0"/>
+        <v>13.936260000000001</v>
+      </c>
+      <c r="D9" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1.62</v>
+      </c>
+      <c r="F9" s="8">
+        <f t="shared" si="1"/>
+        <v>6.6419999999999995</v>
+      </c>
+      <c r="G9" s="8">
+        <v>4.25</v>
+      </c>
+      <c r="H9" s="8">
+        <v>1.621</v>
+      </c>
+      <c r="I9" s="8">
+        <f t="shared" si="2"/>
+        <v>6.8892499999999997</v>
+      </c>
+      <c r="J9" s="8">
+        <f t="shared" si="3"/>
+        <v>13.936260000000001</v>
+      </c>
+      <c r="K9" s="8">
+        <f t="shared" si="4"/>
+        <v>13.53125</v>
+      </c>
+      <c r="L9" s="4">
+        <f t="shared" si="5"/>
+        <v>0.97093840097701956</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
+        <v>10.83</v>
+      </c>
+      <c r="B10" s="8">
+        <v>2.004</v>
+      </c>
+      <c r="C10" s="8">
+        <f t="shared" si="0"/>
+        <v>21.703320000000001</v>
+      </c>
+      <c r="D10" s="8">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="E10" s="8">
+        <v>2.476</v>
+      </c>
+      <c r="F10" s="8">
+        <f t="shared" si="1"/>
+        <v>10.275400000000001</v>
+      </c>
+      <c r="G10" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="H10" s="8">
+        <v>2.4780000000000002</v>
+      </c>
+      <c r="I10" s="8">
+        <f t="shared" si="2"/>
+        <v>10.6554</v>
+      </c>
+      <c r="J10" s="8">
+        <f t="shared" si="3"/>
+        <v>21.703320000000001</v>
+      </c>
+      <c r="K10" s="8">
+        <f t="shared" si="4"/>
+        <v>20.930800000000001</v>
+      </c>
+      <c r="L10" s="4">
+        <f t="shared" si="5"/>
+        <v>0.964405445802762</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="8">
+        <v>11.05</v>
+      </c>
+      <c r="B11" s="8">
+        <v>2.5190000000000001</v>
+      </c>
+      <c r="C11" s="8">
+        <f t="shared" si="0"/>
+        <v>27.834950000000003</v>
+      </c>
+      <c r="D11" s="8">
+        <v>4.16</v>
+      </c>
+      <c r="E11" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="F11" s="8">
+        <f t="shared" si="1"/>
+        <v>12.896000000000001</v>
+      </c>
+      <c r="G11" s="8">
+        <v>4.33</v>
+      </c>
+      <c r="H11" s="8">
+        <v>3.1030000000000002</v>
+      </c>
+      <c r="I11" s="8">
+        <f t="shared" si="2"/>
+        <v>13.43599</v>
+      </c>
+      <c r="J11" s="8">
+        <f t="shared" si="3"/>
+        <v>27.834950000000003</v>
+      </c>
+      <c r="K11" s="8">
+        <f t="shared" si="4"/>
+        <v>26.331990000000001</v>
+      </c>
+      <c r="L11" s="4">
+        <f t="shared" si="5"/>
+        <v>0.94600457338705468</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="8">
+        <v>11.26</v>
+      </c>
+      <c r="B12" s="8">
+        <v>2.996</v>
+      </c>
+      <c r="C12" s="8">
+        <f t="shared" si="0"/>
+        <v>33.734960000000001</v>
+      </c>
+      <c r="D12" s="8">
+        <v>4.24</v>
+      </c>
+      <c r="E12" s="8">
+        <v>3.7090000000000001</v>
+      </c>
+      <c r="F12" s="8">
+        <f t="shared" si="1"/>
+        <v>15.726160000000002</v>
+      </c>
+      <c r="G12" s="8">
+        <v>4.42</v>
+      </c>
+      <c r="H12" s="8">
+        <v>3.7120000000000002</v>
+      </c>
+      <c r="I12" s="8">
+        <f t="shared" si="2"/>
+        <v>16.407040000000002</v>
+      </c>
+      <c r="J12" s="8">
+        <f t="shared" si="3"/>
+        <v>33.734960000000001</v>
+      </c>
+      <c r="K12" s="8">
+        <f t="shared" si="4"/>
+        <v>32.133200000000002</v>
+      </c>
+      <c r="L12" s="4">
+        <f t="shared" si="5"/>
+        <v>0.95251928563128585</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="8">
+        <v>11.35</v>
+      </c>
+      <c r="B13" s="8">
+        <v>3.206</v>
+      </c>
+      <c r="C13" s="8">
+        <f t="shared" si="0"/>
+        <v>36.388100000000001</v>
+      </c>
+      <c r="D13" s="8">
+        <v>4.24</v>
+      </c>
+      <c r="E13" s="8">
+        <v>3.968</v>
+      </c>
+      <c r="F13" s="8">
+        <f t="shared" si="1"/>
+        <v>16.82432</v>
+      </c>
+      <c r="G13" s="8">
+        <v>4.43</v>
+      </c>
+      <c r="H13" s="8">
+        <v>3.972</v>
+      </c>
+      <c r="I13" s="8">
+        <f t="shared" si="2"/>
+        <v>17.595959999999998</v>
+      </c>
+      <c r="J13" s="8">
+        <f t="shared" si="3"/>
+        <v>36.388100000000001</v>
+      </c>
+      <c r="K13" s="8">
+        <f t="shared" si="4"/>
+        <v>34.420279999999998</v>
+      </c>
+      <c r="L13" s="4">
+        <f t="shared" si="5"/>
+        <v>0.94592133142428425</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="8">
+        <v>10.24</v>
+      </c>
+      <c r="B14" s="8">
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="C14" s="8">
+        <f t="shared" si="0"/>
+        <v>9.8611199999999997</v>
+      </c>
+      <c r="D14" s="8">
+        <v>4.05</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1.0609999999999999</v>
+      </c>
+      <c r="F14" s="8">
+        <f t="shared" si="1"/>
+        <v>4.2970499999999996</v>
+      </c>
+      <c r="G14" s="8">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="H14" s="8">
+        <v>1.032</v>
+      </c>
+      <c r="I14" s="8">
+        <f t="shared" si="2"/>
+        <v>4.1899199999999999</v>
+      </c>
+      <c r="J14" s="8">
+        <f t="shared" si="3"/>
+        <v>9.8611199999999997</v>
+      </c>
+      <c r="K14" s="8">
+        <f t="shared" si="4"/>
+        <v>8.4869699999999995</v>
+      </c>
+      <c r="L14" s="4">
+        <f t="shared" si="5"/>
+        <v>0.86064970307632394</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="4"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="4"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="9">
+        <v>10.35</v>
+      </c>
+      <c r="B17" s="9">
+        <v>0.79</v>
+      </c>
+      <c r="C17" s="9">
+        <f t="shared" si="0"/>
+        <v>8.1765000000000008</v>
+      </c>
+      <c r="D17" s="9">
+        <v>4.05</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0.96</v>
+      </c>
+      <c r="F17" s="9">
+        <f t="shared" si="1"/>
+        <v>3.8879999999999999</v>
+      </c>
+      <c r="G17" s="9">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="H17" s="9">
+        <v>0.96</v>
+      </c>
+      <c r="I17" s="9">
+        <f t="shared" si="2"/>
+        <v>3.8975999999999993</v>
+      </c>
+      <c r="J17" s="9">
+        <f t="shared" si="3"/>
+        <v>8.1765000000000008</v>
+      </c>
+      <c r="K17" s="9">
+        <f t="shared" si="4"/>
+        <v>7.7855999999999987</v>
+      </c>
+      <c r="L17" s="4">
+        <f t="shared" si="5"/>
+        <v>0.95219225830122889</v>
+      </c>
+      <c r="M17">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="9">
+        <v>10.73</v>
+      </c>
+      <c r="B18" s="9">
+        <v>1.6</v>
+      </c>
+      <c r="C18" s="9">
+        <f t="shared" ref="C18:C34" si="6">A18*B18</f>
+        <v>17.168000000000003</v>
+      </c>
+      <c r="D18" s="9">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E18" s="9">
+        <v>1.9750000000000001</v>
+      </c>
+      <c r="F18" s="9">
+        <f t="shared" ref="F18:F34" si="7">D18*E18</f>
+        <v>8.0975000000000001</v>
+      </c>
+      <c r="G18" s="9">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="H18" s="9">
+        <v>1.972</v>
+      </c>
+      <c r="I18" s="9">
+        <f t="shared" ref="I18:I33" si="8">G18*H18</f>
+        <v>8.1049199999999999</v>
+      </c>
+      <c r="J18" s="9">
+        <f t="shared" ref="J18:J34" si="9">C18</f>
+        <v>17.168000000000003</v>
+      </c>
+      <c r="K18" s="9">
+        <f t="shared" ref="K18:K33" si="10">F18+I18</f>
+        <v>16.20242</v>
+      </c>
+      <c r="L18" s="4">
+        <f t="shared" ref="L18:L34" si="11">K18/J18</f>
+        <v>0.94375698974836886</v>
+      </c>
+      <c r="M18">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="9">
+        <v>11.13</v>
+      </c>
+      <c r="B19" s="9">
+        <v>2.5</v>
+      </c>
+      <c r="C19" s="9">
+        <f t="shared" si="6"/>
+        <v>27.825000000000003</v>
+      </c>
+      <c r="D19" s="9">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="E19" s="9">
+        <v>3.11</v>
+      </c>
+      <c r="F19" s="9">
+        <f t="shared" si="7"/>
+        <v>12.875399999999999</v>
+      </c>
+      <c r="G19" s="9">
+        <v>4.17</v>
+      </c>
+      <c r="H19" s="9">
+        <v>3.17</v>
+      </c>
+      <c r="I19" s="9">
+        <f t="shared" si="8"/>
+        <v>13.2189</v>
+      </c>
+      <c r="J19" s="9">
+        <f t="shared" si="9"/>
+        <v>27.825000000000003</v>
+      </c>
+      <c r="K19" s="9">
+        <f t="shared" si="10"/>
+        <v>26.094299999999997</v>
+      </c>
+      <c r="L19" s="4">
+        <f t="shared" si="11"/>
+        <v>0.93780053908355776</v>
+      </c>
+      <c r="M19">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="9">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="9">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="4" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="9">
+        <v>10.34</v>
+      </c>
+      <c r="B21" s="9">
+        <v>0.82399999999999995</v>
+      </c>
+      <c r="C21" s="9">
+        <f t="shared" si="6"/>
+        <v>8.5201599999999988</v>
+      </c>
+      <c r="D21" s="9">
+        <v>4.05</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0.998</v>
+      </c>
+      <c r="F21" s="9">
+        <f t="shared" si="7"/>
+        <v>4.0419</v>
+      </c>
+      <c r="G21" s="9">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="H21" s="9">
+        <v>0.995</v>
+      </c>
+      <c r="I21" s="9">
+        <f t="shared" si="8"/>
+        <v>4.0396999999999998</v>
+      </c>
+      <c r="J21" s="9">
+        <f t="shared" si="9"/>
+        <v>8.5201599999999988</v>
+      </c>
+      <c r="K21" s="9">
+        <f t="shared" si="10"/>
+        <v>8.0815999999999999</v>
+      </c>
+      <c r="L21" s="4">
+        <f t="shared" si="11"/>
+        <v>0.94852678822932912</v>
+      </c>
+      <c r="M21">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="9">
+        <v>10.68</v>
+      </c>
+      <c r="B22" s="9">
+        <v>1.63</v>
+      </c>
+      <c r="C22" s="9">
+        <f t="shared" si="6"/>
+        <v>17.408399999999997</v>
+      </c>
+      <c r="D22" s="9">
+        <v>4.0949999999999998</v>
+      </c>
+      <c r="E22" s="9">
+        <v>2.004</v>
+      </c>
+      <c r="F22" s="9">
+        <f t="shared" si="7"/>
+        <v>8.2063799999999993</v>
+      </c>
+      <c r="G22" s="9">
+        <v>4.1139999999999999</v>
+      </c>
+      <c r="H22" s="9">
+        <v>2.004</v>
+      </c>
+      <c r="I22" s="9">
+        <f t="shared" si="8"/>
+        <v>8.2444559999999996</v>
+      </c>
+      <c r="J22" s="9">
+        <f t="shared" si="9"/>
+        <v>17.408399999999997</v>
+      </c>
+      <c r="K22" s="9">
+        <f t="shared" si="10"/>
+        <v>16.450835999999999</v>
+      </c>
+      <c r="L22" s="4">
+        <f t="shared" si="11"/>
+        <v>0.94499414075963339</v>
+      </c>
+      <c r="M22">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="9">
+        <v>11.113</v>
+      </c>
+      <c r="B23" s="9">
+        <v>2.6389999999999998</v>
+      </c>
+      <c r="C23" s="9">
+        <f t="shared" si="6"/>
+        <v>29.327206999999998</v>
+      </c>
+      <c r="D23" s="9">
+        <v>4.1470000000000002</v>
+      </c>
+      <c r="E23" s="9">
+        <v>3.2650000000000001</v>
+      </c>
+      <c r="F23" s="9">
+        <f t="shared" si="7"/>
+        <v>13.539955000000001</v>
+      </c>
+      <c r="G23" s="9">
+        <v>4.1760000000000002</v>
+      </c>
+      <c r="H23" s="9">
+        <v>3.2669999999999999</v>
+      </c>
+      <c r="I23" s="9">
+        <f t="shared" si="8"/>
+        <v>13.642992</v>
+      </c>
+      <c r="J23" s="9">
+        <f t="shared" si="9"/>
+        <v>29.327206999999998</v>
+      </c>
+      <c r="K23" s="9">
+        <f t="shared" si="10"/>
+        <v>27.182946999999999</v>
+      </c>
+      <c r="L23" s="4">
+        <f t="shared" si="11"/>
+        <v>0.92688495702983242</v>
+      </c>
+      <c r="M23">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="9">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="9">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="4" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="9">
+        <v>10.256</v>
+      </c>
+      <c r="B25" s="9">
+        <v>0.621</v>
+      </c>
+      <c r="C25" s="9">
+        <f t="shared" si="6"/>
+        <v>6.368976</v>
+      </c>
+      <c r="D25" s="9">
+        <v>4.0410000000000004</v>
+      </c>
+      <c r="E25" s="9">
+        <v>0.78452</v>
+      </c>
+      <c r="F25" s="9">
+        <f t="shared" si="7"/>
+        <v>3.1702453200000003</v>
+      </c>
+      <c r="G25" s="9">
+        <v>4.0519999999999996</v>
+      </c>
+      <c r="H25" s="9">
+        <v>0.74270000000000003</v>
+      </c>
+      <c r="I25" s="9">
+        <f t="shared" si="8"/>
+        <v>3.0094203999999998</v>
+      </c>
+      <c r="J25" s="9">
+        <f t="shared" si="9"/>
+        <v>6.368976</v>
+      </c>
+      <c r="K25" s="9">
+        <f t="shared" si="10"/>
+        <v>6.17966572</v>
+      </c>
+      <c r="L25" s="4">
+        <f t="shared" si="11"/>
+        <v>0.97027618254488635</v>
+      </c>
+      <c r="M25">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="9">
+        <v>10.428000000000001</v>
+      </c>
+      <c r="B26" s="9">
+        <v>1.0209999999999999</v>
+      </c>
+      <c r="C26" s="9">
+        <f t="shared" si="6"/>
+        <v>10.646988</v>
+      </c>
+      <c r="D26" s="9">
+        <v>4.0609999999999999</v>
+      </c>
+      <c r="E26" s="9">
+        <v>1.244</v>
+      </c>
+      <c r="F26" s="9">
+        <f t="shared" si="7"/>
+        <v>5.0518840000000003</v>
+      </c>
+      <c r="G26" s="9">
+        <v>4.0789999999999997</v>
+      </c>
+      <c r="H26" s="9">
+        <v>1.242</v>
+      </c>
+      <c r="I26" s="9">
+        <f t="shared" si="8"/>
+        <v>5.0661179999999995</v>
+      </c>
+      <c r="J26" s="9">
+        <f t="shared" si="9"/>
+        <v>10.646988</v>
+      </c>
+      <c r="K26" s="9">
+        <f t="shared" si="10"/>
+        <v>10.118002000000001</v>
+      </c>
+      <c r="L26" s="4">
+        <f t="shared" si="11"/>
+        <v>0.95031590154887002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="9">
+        <v>10.683999999999999</v>
+      </c>
+      <c r="B27" s="9">
+        <v>1.623</v>
+      </c>
+      <c r="C27" s="9">
+        <f t="shared" si="6"/>
+        <v>17.340132000000001</v>
+      </c>
+      <c r="D27" s="9">
+        <v>4.0919999999999996</v>
+      </c>
+      <c r="E27" s="9">
+        <v>1.9930000000000001</v>
+      </c>
+      <c r="F27" s="9">
+        <f t="shared" si="7"/>
+        <v>8.1553559999999994</v>
+      </c>
+      <c r="G27" s="9">
+        <v>4.12</v>
+      </c>
+      <c r="H27" s="9">
+        <v>1.9930000000000001</v>
+      </c>
+      <c r="I27" s="9">
+        <f t="shared" si="8"/>
+        <v>8.2111600000000013</v>
+      </c>
+      <c r="J27" s="9">
+        <f t="shared" si="9"/>
+        <v>17.340132000000001</v>
+      </c>
+      <c r="K27" s="9">
+        <f t="shared" si="10"/>
+        <v>16.366516000000001</v>
+      </c>
+      <c r="L27" s="4">
+        <f t="shared" si="11"/>
+        <v>0.94385186917838915</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="9">
+        <v>10.855</v>
+      </c>
+      <c r="B28" s="9">
+        <v>2.0329999999999999</v>
+      </c>
+      <c r="C28" s="9">
+        <f t="shared" si="6"/>
+        <v>22.068214999999999</v>
+      </c>
+      <c r="D28" s="9">
+        <v>4.1150000000000002</v>
+      </c>
+      <c r="E28" s="9">
+        <v>2.5049999999999999</v>
+      </c>
+      <c r="F28" s="9">
+        <f t="shared" si="7"/>
+        <v>10.308075000000001</v>
+      </c>
+      <c r="G28" s="9">
+        <v>4.1479999999999997</v>
+      </c>
+      <c r="H28" s="9">
+        <v>2.5049999999999999</v>
+      </c>
+      <c r="I28" s="9">
+        <f t="shared" si="8"/>
+        <v>10.390739999999999</v>
+      </c>
+      <c r="J28" s="9">
+        <f t="shared" si="9"/>
+        <v>22.068214999999999</v>
+      </c>
+      <c r="K28" s="9">
+        <f t="shared" si="10"/>
+        <v>20.698815</v>
+      </c>
+      <c r="L28" s="4">
+        <f t="shared" si="11"/>
+        <v>0.93794695221158586</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="9">
+        <v>11.11</v>
+      </c>
+      <c r="B29" s="9">
+        <v>2.6360000000000001</v>
+      </c>
+      <c r="C29" s="9">
+        <f t="shared" si="6"/>
+        <v>29.285959999999999</v>
+      </c>
+      <c r="D29" s="9">
+        <v>4.1459999999999999</v>
+      </c>
+      <c r="E29" s="9">
+        <v>3.258</v>
+      </c>
+      <c r="F29" s="9">
+        <f t="shared" si="7"/>
+        <v>13.507667999999999</v>
+      </c>
+      <c r="G29" s="9">
+        <v>4.1879999999999997</v>
+      </c>
+      <c r="H29" s="9">
+        <v>3.258</v>
+      </c>
+      <c r="I29" s="9">
+        <f t="shared" si="8"/>
+        <v>13.644504</v>
+      </c>
+      <c r="J29" s="9">
+        <f t="shared" si="9"/>
+        <v>29.285959999999999</v>
+      </c>
+      <c r="K29" s="9">
+        <f t="shared" si="10"/>
+        <v>27.152172</v>
+      </c>
+      <c r="L29" s="4">
+        <f t="shared" si="11"/>
+        <v>0.92713955765834555</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="9">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="9">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="4" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="9">
+        <v>11.11</v>
+      </c>
+      <c r="B31" s="9">
+        <v>2.645</v>
+      </c>
+      <c r="C31" s="9">
+        <f t="shared" si="6"/>
+        <v>29.385949999999998</v>
+      </c>
+      <c r="D31" s="9">
+        <v>4.6420000000000003</v>
+      </c>
+      <c r="E31" s="9">
+        <v>3.2650000000000001</v>
+      </c>
+      <c r="F31" s="9">
+        <f t="shared" si="7"/>
+        <v>15.156130000000001</v>
+      </c>
+      <c r="G31" s="9">
+        <v>3.69</v>
+      </c>
+      <c r="H31" s="9">
+        <v>3.2770000000000001</v>
+      </c>
+      <c r="I31" s="9">
+        <f t="shared" si="8"/>
+        <v>12.092130000000001</v>
+      </c>
+      <c r="J31" s="9">
+        <f t="shared" si="9"/>
+        <v>29.385949999999998</v>
+      </c>
+      <c r="K31" s="9">
+        <f t="shared" si="10"/>
+        <v>27.248260000000002</v>
+      </c>
+      <c r="L31" s="4">
+        <f t="shared" si="11"/>
+        <v>0.92725469144267936</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="9">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="9">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="4" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="9">
+        <v>10.64</v>
+      </c>
+      <c r="B33" s="9">
+        <v>1.7769999999999999</v>
+      </c>
+      <c r="C33" s="9">
+        <f t="shared" si="6"/>
+        <v>18.90728</v>
+      </c>
+      <c r="D33" s="9">
+        <v>8.14</v>
+      </c>
+      <c r="E33" s="9">
+        <v>2.1850000000000001</v>
+      </c>
+      <c r="F33" s="9">
+        <f t="shared" si="7"/>
+        <v>17.785900000000002</v>
+      </c>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="9">
+        <f t="shared" si="9"/>
+        <v>18.90728</v>
+      </c>
+      <c r="K33" s="9">
+        <f t="shared" si="10"/>
+        <v>17.785900000000002</v>
+      </c>
+      <c r="L33" s="4">
+        <f t="shared" si="11"/>
+        <v>0.94069056998150979</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="10">
+        <v>12.292</v>
+      </c>
+      <c r="B34" s="10">
+        <v>2.3580000000000001</v>
+      </c>
+      <c r="C34" s="10">
+        <f t="shared" si="6"/>
+        <v>28.984536000000002</v>
+      </c>
+      <c r="D34" s="10">
+        <v>9.32</v>
+      </c>
+      <c r="E34" s="10">
+        <v>2.9020000000000001</v>
+      </c>
+      <c r="F34" s="10">
+        <f t="shared" si="7"/>
+        <v>27.046640000000004</v>
+      </c>
+      <c r="G34" s="10">
+        <v>4.0129999999999999</v>
+      </c>
+      <c r="H34">
+        <v>1.4500000000000001E-2</v>
+      </c>
+      <c r="I34" s="10">
+        <f t="shared" ref="I34" si="12">G34*H34</f>
+        <v>5.8188500000000004E-2</v>
+      </c>
+      <c r="J34" s="10">
+        <f t="shared" ref="J34" si="13">C34</f>
+        <v>28.984536000000002</v>
+      </c>
+      <c r="K34" s="10">
+        <f t="shared" ref="K34" si="14">F34+I34</f>
+        <v>27.104828500000004</v>
+      </c>
+      <c r="L34" s="4">
+        <f t="shared" si="11"/>
+        <v>0.93514791818644261</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>